--- a/artfynd/A 36767-2020 artfynd.xlsx
+++ b/artfynd/A 36767-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4371,6 +4371,128 @@
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>62401088</v>
+      </c>
+      <c r="B31" t="n">
+        <v>89747</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>256840</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lilafotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ramaria fennica</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ricken</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Nyborg 1,5 km SO om Läby kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>641975</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6635897</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Läby</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2009-08-31</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2009-08-31</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>4 ex. i vegetationsskikt av kruståtel, vispstarr och väggmossa (tjockt mosstäcke), under gran, i svag sluttning i äldre, grandominerad barrskog.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Äldre, grandominerad barrskog.</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36767-2020 artfynd.xlsx
+++ b/artfynd/A 36767-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36767-2020 artfynd.xlsx
+++ b/artfynd/A 36767-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4361,6 +4361,113 @@
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>122505238</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79945</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>228430</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Rostorangelav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Blastenia ferruginea</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Huds.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Nyborg, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>641938</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6635825</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Läby</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-02-07</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-02-07</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På centimetertjock gren på nyligen fallen halvgrov asp på hygge.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36767-2020 artfynd.xlsx
+++ b/artfynd/A 36767-2020 artfynd.xlsx
@@ -4366,7 +4366,7 @@
         <v>122505238</v>
       </c>
       <c r="B31" t="n">
-        <v>79945</v>
+        <v>79946</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4380,11 +4380,6 @@
       </c>
       <c r="E31" t="n">
         <v>228430</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Rostorangelav</t>
-        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>

--- a/artfynd/A 36767-2020 artfynd.xlsx
+++ b/artfynd/A 36767-2020 artfynd.xlsx
@@ -4366,7 +4366,7 @@
         <v>122505238</v>
       </c>
       <c r="B31" t="n">
-        <v>79946</v>
+        <v>79950</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4380,6 +4380,11 @@
       </c>
       <c r="E31" t="n">
         <v>228430</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Rostorangelav</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>

--- a/artfynd/A 36767-2020 artfynd.xlsx
+++ b/artfynd/A 36767-2020 artfynd.xlsx
@@ -4366,7 +4366,7 @@
         <v>122505238</v>
       </c>
       <c r="B31" t="n">
-        <v>79950</v>
+        <v>79951</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 36767-2020 artfynd.xlsx
+++ b/artfynd/A 36767-2020 artfynd.xlsx
@@ -4366,7 +4366,7 @@
         <v>122505238</v>
       </c>
       <c r="B31" t="n">
-        <v>79951</v>
+        <v>79954</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 36767-2020 artfynd.xlsx
+++ b/artfynd/A 36767-2020 artfynd.xlsx
@@ -4366,7 +4366,7 @@
         <v>122505238</v>
       </c>
       <c r="B31" t="n">
-        <v>79954</v>
+        <v>80056</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 36767-2020 artfynd.xlsx
+++ b/artfynd/A 36767-2020 artfynd.xlsx
@@ -4366,7 +4366,7 @@
         <v>122505238</v>
       </c>
       <c r="B31" t="n">
-        <v>80056</v>
+        <v>80060</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
